--- a/sum.var_AMR_ES_FQ_R.xlsx
+++ b/sum.var_AMR_ES_FQ_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -77,6 +77,75 @@
     <t xml:space="preserve">log_AMC_ville_tot_except_FQ</t>
   </si>
   <si>
+    <t xml:space="preserve">AMR_animaux_compagnie_C3G_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_production_amoxi_clav_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_ES_FQ_R.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">veto_by_CV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tx_possession_chats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tx_possession_chevaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tx_possession_chiens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_SAU_bovine_all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_bovine_all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_bovins_adultes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_livestock_tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_ovins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_porcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_veaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_volailles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_ES_FQ_R.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_NO2_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_O3_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_PM10_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_PM25_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dju_refroi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_i033a_part_class_5_eau_sup_nit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_ES_FQ_R.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">EQI_st</t>
   </si>
   <si>
@@ -92,9 +161,6 @@
     <t xml:space="preserve">unemployement_pourc</t>
   </si>
   <si>
-    <t xml:space="preserve">veto_by_CV</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL_medG</t>
   </si>
   <si>
@@ -107,15 +173,6 @@
     <t xml:space="preserve">couv_creche</t>
   </si>
   <si>
-    <t xml:space="preserve">tx_possession_chats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tx_possession_chevaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tx_possession_chiens</t>
-  </si>
-  <si>
     <t xml:space="preserve">pop_14_moins_prop</t>
   </si>
   <si>
@@ -126,48 +183,6 @@
   </si>
   <si>
     <t xml:space="preserve">log_pop_density</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_NO2_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_O3_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_PM10_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_PM25_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dju_refroi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_i033a_part_class_5_eau_sup_nit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_SAU_bovine_all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_bovine_all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_bovins_adultes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_livestock_tot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_ovins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_porcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_veaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_volailles</t>
   </si>
   <si>
     <t xml:space="preserve">Auvergne-Rhone-Alpes</t>
@@ -689,1901 +704,2096 @@
       <c r="AZ1" t="s">
         <v>51</v>
       </c>
+      <c r="BA1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0101681095327759</v>
+        <v>0.00732955410328057</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.00639006525747155</v>
+        <v>-0.0332116974675727</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00161565964441889</v>
+        <v>0.00673395387442586</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0909191715200746</v>
+        <v>-0.0236791454821986</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0210732090683715</v>
+        <v>-0.0757500947291418</v>
       </c>
       <c r="G2" t="n">
-        <v>0.275510771264029</v>
+        <v>0.0568064656086319</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0789547471719093</v>
+        <v>-0.102978962370727</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.00830864085832837</v>
+        <v>-0.0519636488636131</v>
       </c>
       <c r="J2" t="n">
-        <v>0.130372735547916</v>
+        <v>0.10036063159044</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0702479101048351</v>
+        <v>0.0335610808107989</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0754074413004304</v>
+        <v>0.045746548313324</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0540319841963032</v>
+        <v>-0.0501690072424326</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.170452926298196</v>
+        <v>-0.119218369487267</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0964068146324015</v>
+        <v>-0.0899670434204568</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0768739189200439</v>
+        <v>-0.0729740524328948</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.01995416591953</v>
+        <v>-0.0500340516551097</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.125434614744586</v>
+        <v>-0.11340677064681</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0090841962428216</v>
+        <v>-0.0580919365243204</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0688602337964093</v>
+        <v>0.037870926705233</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.125985988533935</v>
+        <v>-0.114851315499916</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0397566152432577</v>
+        <v>-0.00704050577408892</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0511875566009868</v>
+        <v>-0.0332588684908322</v>
       </c>
       <c r="X2" t="n">
-        <v>0.013543988191261</v>
+        <v>0.00732955410328057</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.0103594589485048</v>
+        <v>0.0582695830019245</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00132232903241835</v>
+        <v>-12.3303494649166</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2214555941569</v>
+        <v>-4.38486917941033</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.131502084188671</v>
+        <v>-18.8678731402826</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.14842969221207</v>
+        <v>0.130610908822835</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.10219512695823</v>
+        <v>0.375555392934203</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0149227985604021</v>
+        <v>0.357498405731887</v>
       </c>
       <c r="AF2" t="n">
-        <v>-13.341163290087</v>
+        <v>0.152621661124171</v>
       </c>
       <c r="AG2" t="n">
-        <v>-4.60423358744294</v>
+        <v>0.150973298446975</v>
       </c>
       <c r="AH2" t="n">
-        <v>-16.4903186411189</v>
+        <v>-0.346688833462624</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.00665697090134184</v>
+        <v>0.235349613528001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.00182643634327915</v>
+        <v>-0.209548982113039</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.00440716000840441</v>
+        <v>0.00732955410328057</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.0648796342378724</v>
+        <v>2.46131616730103</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.29205402211629</v>
+        <v>-2.19227167052624</v>
       </c>
       <c r="AN2" t="n">
-        <v>-2.18228624791595</v>
+        <v>-0.14689466098425</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.237794771894351</v>
+        <v>0.464358721866095</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.576638075921239</v>
+        <v>11.0218902694913</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.07051747799199</v>
+        <v>-0.0137138057235682</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.0126816731330169</v>
+        <v>0.00732955410328057</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.129056967913317</v>
+        <v>-0.0976156339794002</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.388651961036184</v>
+        <v>0.0711842396775379</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.365237339080827</v>
+        <v>0.0133997267485429</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.166629016704061</v>
+        <v>-0.0134887005011725</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.15211795340579</v>
+        <v>-0.0116735390973381</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.318676999390538</v>
+        <v>-0.23814057256977</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.264664015485724</v>
+        <v>0.102157056829545</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.196970110676015</v>
+        <v>0.100964937158633</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.010521087269544</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.00535566593062078</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.00172099403356767</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-0.00508228708977854</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-0.073997723673461</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.0500928710589188</v>
+        <v>-0.0448804961991626</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0385865943219316</v>
+        <v>-0.0269866252159834</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0408477082959145</v>
+        <v>-0.0626853491315937</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0127582139633371</v>
+        <v>0.0667609974418947</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0061906302323655</v>
+        <v>0.00896430553400415</v>
       </c>
       <c r="G3" t="n">
-        <v>0.180439049767516</v>
+        <v>0.0780798483358838</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.056067009215733</v>
+        <v>0.0402110528836817</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000117456787623218</v>
+        <v>0.0110822982171971</v>
       </c>
       <c r="J3" t="n">
-        <v>0.116671964800358</v>
+        <v>0.0352159793973484</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0147152028091843</v>
+        <v>-0.0975259174762126</v>
       </c>
       <c r="L3" t="n">
-        <v>0.140426386283366</v>
+        <v>0.0890607105496024</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00286167012455067</v>
+        <v>-0.0113250537682787</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.00297898990755248</v>
+        <v>0.0302138660849762</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0228788396732879</v>
+        <v>-0.0164060544761927</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00936720902958445</v>
+        <v>0.0138953877725435</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0472777521524752</v>
+        <v>0.0264843564568429</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.00228652309349962</v>
+        <v>0.0155037622756563</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00497417596552354</v>
+        <v>0.0187351769509707</v>
       </c>
       <c r="T3" t="n">
-        <v>0.142399767441171</v>
+        <v>0.0966353497022475</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.00278983832946293</v>
+        <v>0.0175382891813646</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0374249352038843</v>
+        <v>-0.0217683700198446</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.121178699797738</v>
+        <v>0.0791304082566166</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0395432006409371</v>
+        <v>-0.0448804961991626</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.00971601117225818</v>
+        <v>-0.770302815554919</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.00459756815746447</v>
+        <v>3.17771325978908</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.968416707394591</v>
+        <v>9.45590659332335</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.0760140648689032</v>
+        <v>15.5290344904718</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.424655843891086</v>
+        <v>0.0786333169234391</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.0445859523388356</v>
+        <v>0.44603511539236</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.0153001430971059</v>
+        <v>0.420761142313532</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.48006925939705</v>
+        <v>0.117825175411432</v>
       </c>
       <c r="AG3" t="n">
-        <v>9.24627356028839</v>
+        <v>-0.191019448211413</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5796839084115</v>
+        <v>-0.603686124644861</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.00607932817882694</v>
+        <v>0.323806812980551</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.00225351811414473</v>
+        <v>-0.671327616035061</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.00970453867047243</v>
+        <v>-0.0448804961991626</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.751333009804539</v>
+        <v>-1.78849019467855</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1.56519486363179</v>
+        <v>0.594774917323201</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0782585050893027</v>
+        <v>-1.71738724827605</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1.62668796496487</v>
+        <v>-0.472378788154204</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1.02587668462991</v>
+        <v>-5.42457052529447</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-56.5173025440104</v>
+        <v>-0.00784936955362009</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.00198899688420344</v>
+        <v>-0.0448804961991626</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0829289004249411</v>
+        <v>-0.0689272219917101</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.462728832949712</v>
+        <v>-0.124494038406793</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.435909659548074</v>
+        <v>0.0396977072599543</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.133081479181657</v>
+        <v>-0.0114595398085665</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.192975911335374</v>
+        <v>-0.00299484608859408</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.591356816039738</v>
+        <v>-0.0900985847101783</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.338749563388879</v>
+        <v>-0.430405702605618</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.651216767947057</v>
+        <v>-0.0400073610756617</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-0.0209620918427937</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-0.00686645883417283</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-0.00212758389752027</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.00960011029148658</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-0.733223676197547</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0549822360007503</v>
+        <v>-0.0402427339189276</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00504343840223279</v>
+        <v>0.00779730675007682</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.140902417382569</v>
+        <v>-0.0839658046014768</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.168337133756571</v>
+        <v>-0.160573643927154</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.00237992060775575</v>
+        <v>0.0116350506174326</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.250324113835239</v>
+        <v>-0.169554384362192</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0814813442285465</v>
+        <v>0.201525623572652</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0281176982455433</v>
+        <v>-0.0181058995709713</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.346311840554952</v>
+        <v>-0.278648268623139</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.642879976548583</v>
+        <v>-0.37338220636912</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.239735870896834</v>
+        <v>-0.204154783015747</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.109552480845898</v>
+        <v>-0.0988475340227592</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.20394631564326</v>
+        <v>-0.141210710616172</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0873502250456181</v>
+        <v>-0.0466720427614512</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0210555944286251</v>
+        <v>-0.0223308923262131</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0329573621364871</v>
+        <v>0.0503303137154591</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.117152084942448</v>
+        <v>-0.0794524172790022</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0146887323183781</v>
+        <v>-0.00749851703955117</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.227782580329541</v>
+        <v>-0.193174881389105</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.112110867551475</v>
+        <v>-0.0732747438842462</v>
       </c>
       <c r="V4" t="n">
-        <v>0.379388762045197</v>
+        <v>-0.00278835022062918</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0443103727409266</v>
+        <v>-0.0963687065038142</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0188102194090047</v>
+        <v>-0.0402427339189276</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.0321800417758745</v>
+        <v>-0.0055179876751338</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.0104311156910719</v>
+        <v>-3.63618198377684</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0238900220133278</v>
+        <v>3.19198075695889</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.402140825519066</v>
+        <v>12.7284237561243</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.351821654834091</v>
+        <v>0.282585669768487</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.111027664953521</v>
+        <v>1.08459192358979</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.0523720187307831</v>
+        <v>1.08405563486571</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0679736161776323</v>
+        <v>1.69130769280195</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.09609479782495</v>
+        <v>-0.369642789809718</v>
       </c>
       <c r="AH4" t="n">
-        <v>8.88327359528736</v>
+        <v>2.74556373901538</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.00456057800534087</v>
+        <v>0.75630921144054</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.00233350096272741</v>
+        <v>2.08339580005781</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.00507782396868468</v>
+        <v>-0.0402427339189276</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.00737594880441416</v>
+        <v>-4.31875399729239</v>
       </c>
       <c r="AM4" t="n">
-        <v>-3.2580124369192</v>
+        <v>3.56540005694909</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.1455577351123</v>
+        <v>-0.782589675263861</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.208851611857849</v>
+        <v>-1.41801144666476</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.784250969539515</v>
+        <v>-42.063917768553</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-38.6423884162453</v>
+        <v>0.00319752936881097</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.0175895926466468</v>
+        <v>-0.0402427339189276</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.258833341475591</v>
+        <v>0.391618492627779</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.05641992186321</v>
+        <v>-0.0654341902052057</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.06394731766887</v>
+        <v>0.0180099487089462</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.66786584018637</v>
+        <v>-0.0322092704598475</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.349940260924335</v>
+        <v>-0.017640294352863</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.70731797818989</v>
+        <v>0.271938752196663</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.680091244383167</v>
+        <v>0.0988875903309765</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.04958589850437</v>
+        <v>-0.110766501464643</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0.041946136308274</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0.00273756632938549</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0.00197807540185887</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.00639467520062348</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0.00507901594179504</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00377475778197619</v>
+        <v>-0.00323860940402544</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.14880784492609</v>
+        <v>-0.122014764713604</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.111455204064908</v>
+        <v>-0.0980898804713043</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0697147216437513</v>
+        <v>-0.0460995270754599</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.110865132212821</v>
+        <v>-0.0856219006310501</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0127505620390644</v>
+        <v>-0.114016310368139</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.304575801859695</v>
+        <v>-0.169157530573119</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.130889769203881</v>
+        <v>-0.0943666974336294</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0679864283662646</v>
+        <v>-0.046366232871423</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.144587792640908</v>
+        <v>-0.130678648965293</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0918759040919557</v>
+        <v>-0.048917726788189</v>
       </c>
       <c r="M5" t="n">
-        <v>0.00333650988563837</v>
+        <v>-0.026573481692435</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0714115275171248</v>
+        <v>-0.0692464942458135</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0720043166323298</v>
+        <v>-0.0647205616522289</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0511063244009886</v>
+        <v>-0.0278724541611876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0324788645153411</v>
+        <v>-0.0218776303200323</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.0709266527115795</v>
+        <v>-0.0651659970916472</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.129505012074042</v>
+        <v>-0.094704517426158</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0943594389707066</v>
+        <v>-0.0493827395147707</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0747343594340529</v>
+        <v>-0.0662767394077226</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0768779108434883</v>
+        <v>-0.0175848898050814</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.131599358243504</v>
+        <v>-0.000922632744525248</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0247444766973079</v>
+        <v>-0.00323860940402544</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0094975336029343</v>
+        <v>-0.602380310114915</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.0120619122976028</v>
+        <v>12.8592769993275</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.897649899911115</v>
+        <v>-0.192251643736603</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.587606110192973</v>
+        <v>26.77912495624</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.956114604383485</v>
+        <v>-0.197700988707845</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.124474149596459</v>
+        <v>-0.480525696225354</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.0430327999176401</v>
+        <v>-0.491243416945087</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.8246689238084</v>
+        <v>-0.517661915067306</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.190409484003643</v>
+        <v>-0.284096832305203</v>
       </c>
       <c r="AH5" t="n">
-        <v>23.6692783480842</v>
+        <v>-0.268031660005875</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.000942082746216486</v>
+        <v>-0.416594915570839</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.000358143882772694</v>
+        <v>-0.311494422645666</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.00801228791784608</v>
+        <v>-0.00323860940402544</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.635892293686538</v>
+        <v>-3.27804295023073</v>
       </c>
       <c r="AM5" t="n">
-        <v>-2.65288172678463</v>
+        <v>0.103643179064499</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1.14695629389539</v>
+        <v>-1.31587084830012</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1.64106791919975</v>
+        <v>-0.38010878600959</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.247141293132758</v>
+        <v>-6.61747476724499</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-51.9213691303794</v>
+        <v>0.0379833337977912</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0842616923844482</v>
+        <v>-0.00323860940402544</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.18561629713854</v>
+        <v>-0.0623337941018985</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.476927311635216</v>
+        <v>-0.0889789398903094</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.48815939095749</v>
+        <v>0.0267904630273537</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.492049005877399</v>
+        <v>-0.011307532303508</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.255607756724321</v>
+        <v>0.000275088542728966</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.270930852738574</v>
+        <v>-0.498774154428945</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.403407327456097</v>
+        <v>-0.805735820374807</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.20940275639533</v>
+        <v>-0.120788240069277</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-0.0302881325843596</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.0000407778520189205</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-0.000485969982432017</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.00829966907346026</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-0.622655757258443</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0300454589261204</v>
+        <v>0.0196401513701033</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0431004876914876</v>
+        <v>0.110123897161324</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0765988913809954</v>
+        <v>0.0594823394641421</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0964422660822828</v>
+        <v>0.00138620103745199</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.029594416537704</v>
+        <v>-0.0410338671533221</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0863197432598426</v>
+        <v>0.0156302908688696</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0165045557932629</v>
+        <v>-0.0524689124097606</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0277053363830317</v>
+        <v>-0.00777819389424965</v>
       </c>
       <c r="J6" t="n">
-        <v>0.142169977730365</v>
+        <v>0.183072132285433</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.210715590713308</v>
+        <v>-0.0140515295826258</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0575125722774618</v>
+        <v>0.085549861147115</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0454410533552694</v>
+        <v>0.0581279308629707</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0270506640427203</v>
+        <v>0.0594315464166114</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.000864952213764691</v>
+        <v>-0.0139516952096968</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0221035885849275</v>
+        <v>0.0972308094678789</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0282998536188341</v>
+        <v>-0.0395915370136168</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0128419964400081</v>
+        <v>0.0291116808889536</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0398789679573504</v>
+        <v>-0.0130612761644817</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0485171750001827</v>
+        <v>0.070693667754269</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00919580398934066</v>
+        <v>0.0248295369766438</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0147438537452712</v>
+        <v>-0.0202219764604383</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.093984238534703</v>
+        <v>0.0597279019483435</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0177446887300885</v>
+        <v>0.0196401513701033</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.00572093987488779</v>
+        <v>-0.423678741868557</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.000774351135356489</v>
+        <v>-2.61132807038946</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.840932403856773</v>
+        <v>-6.89076795398724</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.154997563564627</v>
+        <v>-29.9470519040486</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.216996359700968</v>
+        <v>-0.0332608460612143</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0390836361218569</v>
+        <v>0.137839947010808</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0333641329899604</v>
+        <v>0.13637941094463</v>
       </c>
       <c r="AF6" t="n">
-        <v>-2.14984573243554</v>
+        <v>-0.122399969203203</v>
       </c>
       <c r="AG6" t="n">
-        <v>-6.70141306059287</v>
+        <v>-0.150794157450055</v>
       </c>
       <c r="AH6" t="n">
-        <v>-26.1854044108079</v>
+        <v>-0.388364951192247</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.00413655181252143</v>
+        <v>-0.0224633016088872</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.000757604010632065</v>
+        <v>-0.595670602562299</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.00735798729403276</v>
+        <v>0.0196401513701033</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.257013136873616</v>
+        <v>0.647163158559724</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.119196013599442</v>
+        <v>-3.1904011933925</v>
       </c>
       <c r="AN6" t="n">
-        <v>-2.28229777734521</v>
+        <v>-0.453595963951475</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.826822763646479</v>
+        <v>0.622946781722748</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.55676328207548</v>
+        <v>-15.8994468340273</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-76.2782317852448</v>
+        <v>-0.00455811689816679</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.00853659344662118</v>
+        <v>0.0196401513701033</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0316000862081029</v>
+        <v>-0.0650535239568293</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.137814729976648</v>
+        <v>-0.0879917342022967</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.137826861336437</v>
+        <v>0.0198687079575747</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.109513409027774</v>
+        <v>0.00373493005830028</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.159576214336439</v>
+        <v>0.00822729452788746</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.372499175882289</v>
+        <v>0.0877323322809686</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.028182694731742</v>
+        <v>-0.190653634970529</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.480913753276149</v>
+        <v>0.0388954366948321</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.0118321019448495</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.00503272571077103</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-0.000799265942887367</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.00593181281709199</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.242091355144987</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0151244682190576</v>
+        <v>0.0188915953450621</v>
       </c>
       <c r="C7" t="n">
-        <v>0.133299759400714</v>
+        <v>0.0554788106625309</v>
       </c>
       <c r="D7" t="n">
-        <v>0.17119308852354</v>
+        <v>0.0614207298724778</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0323065773663209</v>
+        <v>-0.0145088813068838</v>
       </c>
       <c r="F7" t="n">
-        <v>0.144429066652829</v>
+        <v>0.110606121684165</v>
       </c>
       <c r="G7" t="n">
-        <v>0.483272915226141</v>
+        <v>0.250285857549249</v>
       </c>
       <c r="H7" t="n">
-        <v>0.146985012629849</v>
+        <v>0.0680502058653062</v>
       </c>
       <c r="I7" t="n">
-        <v>0.161433084671603</v>
+        <v>0.0918115939259928</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0661231501204807</v>
+        <v>0.0601744798308835</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0464307517052205</v>
+        <v>-0.188331569638821</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0763846257534399</v>
+        <v>0.0406597387657337</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.00290763614771308</v>
+        <v>0.00202098858221799</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0885296988231376</v>
+        <v>0.0874935060532407</v>
       </c>
       <c r="O7" t="n">
-        <v>0.136002148567348</v>
+        <v>0.110979265869809</v>
       </c>
       <c r="P7" t="n">
-        <v>0.049112925889316</v>
+        <v>0.0239107660601627</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0344972370956274</v>
+        <v>0.00273469106055817</v>
       </c>
       <c r="R7" t="n">
-        <v>0.125860386484964</v>
+        <v>0.105554071475889</v>
       </c>
       <c r="S7" t="n">
-        <v>0.156496669451022</v>
+        <v>0.0951759245750315</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0768356453792964</v>
+        <v>0.0383246834572868</v>
       </c>
       <c r="U7" t="n">
-        <v>0.131564649816392</v>
+        <v>0.111511245163811</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.165514779071453</v>
+        <v>-0.000156771078757567</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.131245610350165</v>
+        <v>0.117467098864332</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0107216675089381</v>
+        <v>0.0188915953450621</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0322515223747316</v>
+        <v>0.138826687668009</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0189242026662395</v>
+        <v>-4.93482380993126</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.165680899416274</v>
+        <v>-7.22063560926808</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.385927378853887</v>
+        <v>19.8455533951558</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.630969791295231</v>
+        <v>-0.0180925555466997</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.102581169404778</v>
+        <v>0.418246721515095</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.0412286870027115</v>
+        <v>0.424361583032095</v>
       </c>
       <c r="AF7" t="n">
-        <v>-4.49083738512474</v>
+        <v>0.289059744010996</v>
       </c>
       <c r="AG7" t="n">
-        <v>-6.89728110620884</v>
+        <v>-0.271578415094269</v>
       </c>
       <c r="AH7" t="n">
-        <v>19.5530802323725</v>
+        <v>0.308994584925497</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0153868273184087</v>
+        <v>0.159101834134017</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.00263695192268006</v>
+        <v>0.197995368697023</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.0196088150451624</v>
+        <v>0.0188915953450621</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.404616717504317</v>
+        <v>1.12134033295021</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.39114567473166</v>
+        <v>-5.94298722785559</v>
       </c>
       <c r="AN7" t="n">
-        <v>-5.52228264776844</v>
+        <v>2.15545868450043</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.41813463805371</v>
+        <v>1.54602068082667</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.797262381070981</v>
+        <v>-32.1995523411849</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-75.560468338323</v>
+        <v>-0.0121944982685219</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.010588415429698</v>
+        <v>0.0188915953450621</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.0136057872193962</v>
+        <v>-0.170172304400208</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.429213209606387</v>
+        <v>-0.130900303696153</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.436203429019931</v>
+        <v>-0.0097474141827183</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.310735436489687</v>
+        <v>0.0367801772712077</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.25727729702729</v>
+        <v>0.0262124964709996</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.282686640667764</v>
+        <v>0.357638558366775</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.161679782210722</v>
+        <v>-0.563513299647262</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.293032108704432</v>
+        <v>-0.106189643756344</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0.0501937303954304</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.0165749855340629</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.00341200918641746</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.0185588523633794</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.420820327277151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0568961028167552</v>
+        <v>0.0533533633004615</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.133243265495499</v>
+        <v>-0.134831925330972</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.067806267984099</v>
+        <v>-0.106665696028367</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0734573257731818</v>
+        <v>-0.00210520011203225</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0540924822244721</v>
+        <v>-0.0041952574902393</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.130768518136363</v>
+        <v>-0.11590073157777</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0456285121038076</v>
+        <v>-0.0259083380395657</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0979404923773491</v>
+        <v>-0.0493917054781802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0341105676280771</v>
+        <v>-0.0883645155060498</v>
       </c>
       <c r="K8" t="n">
-        <v>0.296295136930959</v>
+        <v>0.309219299525867</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0583252895641177</v>
+        <v>0.0567337331081234</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0525516031295875</v>
+        <v>-0.0463280683589995</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0438704421428849</v>
+        <v>0.0138111941148235</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0974492495608683</v>
+        <v>0.0861825699207249</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3117942048597</v>
+        <v>0.263100653547779</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0440847692538027</v>
+        <v>0.0241502037875185</v>
       </c>
       <c r="R8" t="n">
-        <v>0.104516109606357</v>
+        <v>0.0823716821161474</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0980459327492597</v>
+        <v>-0.0423401208623003</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0604829063408394</v>
+        <v>0.0757260764774565</v>
       </c>
       <c r="U8" t="n">
-        <v>0.113169120375783</v>
+        <v>0.0918117366690664</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.538533345733852</v>
+        <v>0.0317868662453055</v>
       </c>
       <c r="W8" t="n">
-        <v>0.575259680842664</v>
+        <v>-0.0612103131719041</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.101653350113491</v>
+        <v>0.0533533633004615</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0172839814630385</v>
+        <v>1.71905337412741</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00895536017518011</v>
+        <v>-9.01272307721351</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15902538943919</v>
+        <v>-16.3377612856515</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.517038176738739</v>
+        <v>-92.0387708878531</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.665070740718722</v>
+        <v>-0.324050522133134</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.334194620928908</v>
+        <v>-1.96214937859133</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.11129398891271</v>
+        <v>-1.89546618886632</v>
       </c>
       <c r="AF8" t="n">
-        <v>-22.2623894531407</v>
+        <v>-1.89651190208578</v>
       </c>
       <c r="AG8" t="n">
-        <v>-15.860981596586</v>
+        <v>-0.537245017539383</v>
       </c>
       <c r="AH8" t="n">
-        <v>-92.0946612447093</v>
+        <v>-1.22021097105653</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0165221538736564</v>
+        <v>-1.22631695627796</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.00723657586544204</v>
+        <v>-0.810419476847576</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.0298786520134237</v>
+        <v>0.0533533633004615</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.10139607988036</v>
+        <v>11.0611048510848</v>
       </c>
       <c r="AM8" t="n">
-        <v>8.97208310235245</v>
+        <v>-8.13657157043532</v>
       </c>
       <c r="AN8" t="n">
-        <v>-6.04702387924042</v>
+        <v>1.89965622981696</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.45947344185772</v>
+        <v>1.2231669853248</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.33682725744331</v>
+        <v>-14.3772288344109</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-63.1679710884555</v>
+        <v>0.0167786207189275</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.00985033312017121</v>
+        <v>0.0533533633004615</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0.303602013221618</v>
+        <v>-0.160721921099835</v>
       </c>
       <c r="AT8" t="n">
-        <v>-1.96326622895298</v>
+        <v>0.623368914024887</v>
       </c>
       <c r="AU8" t="n">
-        <v>-1.89514813802743</v>
+        <v>-0.104572526869896</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.86315874323237</v>
+        <v>0.0145650987656854</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.515301230578358</v>
+        <v>-0.00235061950876203</v>
       </c>
       <c r="AX8" t="n">
-        <v>-1.20040223792695</v>
+        <v>-0.364227869492569</v>
       </c>
       <c r="AY8" t="n">
-        <v>-1.18622603079211</v>
+        <v>0.868083983240932</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.707914531381236</v>
+        <v>0.332517882452744</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.103648576807794</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.0175497742443751</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.00697314120095147</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.0301335771134524</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.10000862327134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0457432325885827</v>
+        <v>-0.0383343059783089</v>
       </c>
       <c r="C9" t="n">
-        <v>0.13735670331231</v>
+        <v>0.0694253778846952</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0728050883097026</v>
+        <v>0.0346589884140389</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0988670398412476</v>
+        <v>0.111605333198221</v>
       </c>
       <c r="F9" t="n">
-        <v>0.136523909470992</v>
+        <v>0.0962525363404283</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.137140518417397</v>
+        <v>0.153427391633997</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0382832229863859</v>
+        <v>-0.00746862204342071</v>
       </c>
       <c r="I9" t="n">
-        <v>0.112321840035941</v>
+        <v>0.0855536155303945</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.00253753201355174</v>
+        <v>0.0504734259398501</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.029547409760722</v>
+        <v>-0.208271122741779</v>
       </c>
       <c r="L9" t="n">
-        <v>0.197042698464516</v>
+        <v>0.0986245611203094</v>
       </c>
       <c r="M9" t="n">
-        <v>0.000886637959506379</v>
+        <v>-0.0108437631294407</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0507728550843026</v>
+        <v>0.0786633420934962</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0567438063386301</v>
+        <v>0.0415623718171625</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0209712268648343</v>
+        <v>-0.0324191136737228</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.031111182630161</v>
+        <v>-0.0027053805893549</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0491143324423781</v>
+        <v>0.0383287535447493</v>
       </c>
       <c r="S9" t="n">
-        <v>0.11420954189731</v>
+        <v>0.09066077539429</v>
       </c>
       <c r="T9" t="n">
-        <v>0.218812529751452</v>
+        <v>0.104722423510447</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0512135603807914</v>
+        <v>0.0416848994848347</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0635795932907345</v>
+        <v>-0.00113998729489261</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0845726698805684</v>
+        <v>-0.0674828256708319</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0328097953434456</v>
+        <v>-0.0383343059783089</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.00846694414753739</v>
+        <v>-0.314908419026853</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00136559057441172</v>
+        <v>-0.624784079803963</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.450194963316188</v>
+        <v>24.7971160064304</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0490564449104061</v>
+        <v>21.1224527119021</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.600218877096752</v>
+        <v>0.229753807778225</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.0694742695603066</v>
+        <v>1.05828541957378</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.0526071690728861</v>
+        <v>1.06438261422827</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.819725175862487</v>
+        <v>0.785942009562261</v>
       </c>
       <c r="AG9" t="n">
-        <v>25.0459273505656</v>
+        <v>-0.239068858776235</v>
       </c>
       <c r="AH9" t="n">
-        <v>23.2522214542911</v>
+        <v>0.487882730365099</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.00157097117526957</v>
+        <v>0.697195612240213</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.000289284620925843</v>
+        <v>-0.0374455911788562</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.00108999354064878</v>
+        <v>-0.0383343059783089</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.114965393568865</v>
+        <v>-1.67028852900829</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.583082910914034</v>
+        <v>-0.0109312412913779</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.407497664271175</v>
+        <v>-0.191921675231057</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.626052682150197</v>
+        <v>-0.336248048840461</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0769439854587758</v>
+        <v>-38.3424138223202</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-65.8116411525116</v>
+        <v>-0.00107446016607559</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.0168580684837055</v>
+        <v>-0.0383343059783089</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.219666937238778</v>
+        <v>0.074872943332801</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.05843083640591</v>
+        <v>-0.085804112752481</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.06619759209827</v>
+        <v>0.0321586612015137</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.785189420817468</v>
+        <v>-0.00673117719952007</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.265401738115987</v>
+        <v>0.00173258813346108</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.467360038785002</v>
+        <v>-0.0206447053958451</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.680302987094055</v>
+        <v>-0.56047013214129</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.0291130667848808</v>
+        <v>-0.0657887445398481</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-0.0496410442958685</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.00197200880993254</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-0.000229650166180577</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.000208184884516435</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-0.10211662579286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.015289439297142</v>
+        <v>-0.00601199919180279</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1315516774714</v>
+        <v>0.194361998892864</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0527355116617763</v>
+        <v>0.0975994435577037</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0334283093909175</v>
+        <v>0.0233719976102421</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00042985079174807</v>
+        <v>0.0395856823912233</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0886760572972263</v>
+        <v>0.0123800376221514</v>
       </c>
       <c r="H10" t="n">
-        <v>0.110265643614896</v>
+        <v>0.0698733751954535</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0481502356380523</v>
+        <v>0.0705558338791445</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0522154116731337</v>
+        <v>0.0849547857042242</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0825817721032198</v>
+        <v>0.0601430323680632</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0376081186568276</v>
+        <v>0.0292138845299469</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0410385396655344</v>
+        <v>0.0660182326205712</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0205163929407754</v>
+        <v>0.00620438066090511</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0291694426370736</v>
+        <v>0.0307882196430586</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0468863991315012</v>
+        <v>-0.0506951096157239</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0474267900507508</v>
+        <v>0.013325731189545</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0291388278397692</v>
+        <v>0.0325507305764863</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0460851125528593</v>
+        <v>0.0637311713530358</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0480349636525231</v>
+        <v>0.0218218940632773</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0268978118133331</v>
+        <v>0.0274333514639498</v>
       </c>
       <c r="V10" t="n">
-        <v>0.219368756877924</v>
+        <v>-0.00351881208243151</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0760827716033757</v>
+        <v>0.000139235351569367</v>
       </c>
       <c r="X10" t="n">
-        <v>0.00501146517497959</v>
+        <v>-0.00601199919180279</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.00746694442030418</v>
+        <v>-0.317730159419209</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.000195010590825256</v>
+        <v>9.18564175834393</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.404656722171274</v>
+        <v>2.60351806295416</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.210037148550869</v>
+        <v>38.9228280039465</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.384491133118607</v>
+        <v>-0.0079908077062404</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.104804421541471</v>
+        <v>0.0993371854900619</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.0174401747865832</v>
+        <v>0.0648298521035288</v>
       </c>
       <c r="AF10" t="n">
-        <v>11.5566978171903</v>
+        <v>0.120572232824682</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.20110036158925</v>
+        <v>0.598748291963005</v>
       </c>
       <c r="AH10" t="n">
-        <v>38.8507503444811</v>
+        <v>-0.117960350491315</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.0156954258359246</v>
+        <v>0.0824821535077846</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.00381859147964579</v>
+        <v>0.322043412432475</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.014541869119221</v>
+        <v>-0.00601199919180279</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.535255627652924</v>
+        <v>-3.36054905774655</v>
       </c>
       <c r="AM10" t="n">
-        <v>-3.09709409151426</v>
+        <v>0.125640023711585</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.681519922851336</v>
+        <v>-1.05862112080309</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.293785645346047</v>
+        <v>-0.969569942067806</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.564041971973848</v>
+        <v>20.4716391934634</v>
       </c>
       <c r="AQ10" t="n">
-        <v>81.6554628857415</v>
+        <v>0.00616639835771458</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.00797011606841954</v>
+        <v>-0.00601199919180279</v>
       </c>
       <c r="AS10" t="n">
-        <v>-0.013491713720902</v>
+        <v>0.123513363905274</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0677816138142525</v>
+        <v>-0.0682606175468987</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.0300130308943995</v>
+        <v>0.00640762906621618</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0455964636090386</v>
+        <v>-0.00569589876732141</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.586357465418957</v>
+        <v>-0.00231622520835979</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.0789601941387245</v>
+        <v>0.226721715917034</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.06787968204752</v>
+        <v>0.255688366175892</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0551690670130849</v>
+        <v>-0.106329782035779</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.000487602492993006</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-0.01638452748375</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-0.00423125097371813</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.0154679259900934</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-0.544121789461287</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0333209740529657</v>
+        <v>0.0190675251908354</v>
       </c>
       <c r="C11" t="n">
-        <v>0.037105010608997</v>
+        <v>0.147380940790155</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0412759617004496</v>
+        <v>0.0860160295965499</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0922539839363019</v>
+        <v>0.02995211991031</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0119852366423621</v>
+        <v>0.00953556340121431</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.161406874562642</v>
+        <v>-0.0663141535071389</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0221185370221191</v>
+        <v>0.0558181981008451</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.000889523093469356</v>
+        <v>0.0296954906944263</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0571596524101275</v>
+        <v>0.0158617624856274</v>
       </c>
       <c r="K11" t="n">
-        <v>0.517742025183917</v>
+        <v>0.313060253546427</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.017198197483184</v>
+        <v>-0.0427652547046527</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0896073579293092</v>
+        <v>0.109958567821692</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0703699928422246</v>
+        <v>0.042769586516405</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0133406990232049</v>
+        <v>0.0211958266043548</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.0479831217721902</v>
+        <v>-0.0434899261813493</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.0403632081502677</v>
+        <v>-0.000646349904212877</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0231943288193214</v>
+        <v>0.03321280075391</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.00578151363316655</v>
+        <v>0.0240534255699838</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0114233476468113</v>
+        <v>-0.0505408090917457</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0157477556104042</v>
+        <v>0.0233233898465209</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0969169401982043</v>
+        <v>-0.0160402896903781</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.108103245075584</v>
+        <v>0.1346138312419</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.0255203914525662</v>
+        <v>0.0190675251908354</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0299772394255812</v>
+        <v>0.128949509529747</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.011348429902456</v>
+        <v>6.42513956495643</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.505887118535677</v>
+        <v>-3.78655200623572</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.0390253217259621</v>
+        <v>28.9449742236903</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.440605472901525</v>
+        <v>-0.0951203534760066</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.00658137879622107</v>
+        <v>-0.280465339930393</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0272621529589622</v>
+        <v>-0.315517269456471</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.13294823737179</v>
+        <v>-0.268724626977033</v>
       </c>
       <c r="AG11" t="n">
-        <v>-4.02955524163182</v>
+        <v>0.975430705687471</v>
       </c>
       <c r="AH11" t="n">
-        <v>26.0949576352228</v>
+        <v>-0.489446482450284</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.00877873672467052</v>
+        <v>-0.198475120765655</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.00201849525805852</v>
+        <v>-0.48313178901756</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.00899842736562835</v>
+        <v>0.0190675251908354</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.39598139848856</v>
+        <v>-1.42640909208072</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1.44475168581621</v>
+        <v>5.91211095973774</v>
       </c>
       <c r="AN11" t="n">
-        <v>4.21650986320368</v>
+        <v>-0.895613718645758</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.423515374453965</v>
+        <v>-0.823422918814776</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.019995535278604</v>
+        <v>64.7608500031866</v>
       </c>
       <c r="AQ11" t="n">
-        <v>180.356074231814</v>
+        <v>-0.00583898559699208</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.000336264258644064</v>
+        <v>0.0190675251908354</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0.0941840750332146</v>
+        <v>0.0725586485713087</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0.295811437285488</v>
+        <v>-0.0794686588701281</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.336460793504105</v>
+        <v>-0.022730959003571</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.296791474770966</v>
+        <v>0.028768876407479</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.935955562839494</v>
+        <v>0.00562799823828984</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.492886113912943</v>
+        <v>0.132832947960337</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.187599762124215</v>
+        <v>0.482211586012499</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.591612753676818</v>
+        <v>-0.00974559752949912</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.0316327784762719</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0.0103886763340441</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0.00230109366776357</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.00888449742549417</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0.416902965091475</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0318291802988201</v>
+        <v>0.0344414747163138</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0628056004575364</v>
+        <v>0.0627569214130735</v>
       </c>
       <c r="D12" t="n">
-        <v>0.184904568386425</v>
+        <v>0.16928729582152</v>
       </c>
       <c r="E12" t="n">
-        <v>0.486930072918561</v>
+        <v>0.181161651205074</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0590659590540827</v>
+        <v>0.0151993913420284</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0984111716925415</v>
+        <v>-0.049942846229566</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0276609438400922</v>
+        <v>0.0337106585056498</v>
       </c>
       <c r="I12" t="n">
-        <v>0.127106051535496</v>
+        <v>0.0663592388653425</v>
       </c>
       <c r="J12" t="n">
-        <v>0.150818965563842</v>
+        <v>0.12082021118173</v>
       </c>
       <c r="K12" t="n">
-        <v>0.401273979811799</v>
+        <v>0.467253145695357</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0679124601791692</v>
+        <v>0.0122705756134747</v>
       </c>
       <c r="M12" t="n">
-        <v>0.140603337614277</v>
+        <v>0.131205113193585</v>
       </c>
       <c r="N12" t="n">
-        <v>0.417360756755521</v>
+        <v>0.198025239949699</v>
       </c>
       <c r="O12" t="n">
-        <v>0.109499327541346</v>
+        <v>0.0571106148616265</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0152764714191819</v>
+        <v>-0.00197631555638445</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0425659793365822</v>
+        <v>0.0331111192044257</v>
       </c>
       <c r="R12" t="n">
-        <v>0.179730939186457</v>
+        <v>0.094141686407852</v>
       </c>
       <c r="S12" t="n">
-        <v>0.116756097647197</v>
+        <v>0.0506071158844021</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0917143847535551</v>
+        <v>-0.00172738073185696</v>
       </c>
       <c r="U12" t="n">
-        <v>0.175832658049682</v>
+        <v>0.0855989607660336</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.220429414399025</v>
+        <v>0.0325476245037432</v>
       </c>
       <c r="W12" t="n">
-        <v>0.165002681686222</v>
+        <v>-0.0634160524993205</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.0561219478419011</v>
+        <v>0.0344414747163138</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0281326728154699</v>
+        <v>1.02430888453424</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.00455406525236886</v>
+        <v>10.3825789897294</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5213958373297</v>
+        <v>-11.8074921105374</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.307852760724504</v>
+        <v>-12.7054687916566</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.29212768055983</v>
+        <v>-0.280826175534107</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.199083287136118</v>
+        <v>-1.96187907500934</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0646274834494113</v>
+        <v>-1.89482506440636</v>
       </c>
       <c r="AF12" t="n">
-        <v>4.35404963718029</v>
+        <v>-1.59565512176468</v>
       </c>
       <c r="AG12" t="n">
-        <v>-11.4882731016136</v>
+        <v>0.615213205875665</v>
       </c>
       <c r="AH12" t="n">
-        <v>-13.2887291233021</v>
+        <v>-1.18205595693551</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.00805098770196485</v>
+        <v>-1.22766947552045</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.000376303410427653</v>
+        <v>-1.35410658786014</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0165819858955276</v>
+        <v>0.0344414747163138</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.274049575007943</v>
+        <v>4.24082559502784</v>
       </c>
       <c r="AM12" t="n">
-        <v>3.9146093859639</v>
+        <v>6.72187461778694</v>
       </c>
       <c r="AN12" t="n">
-        <v>8.51528279800994</v>
+        <v>3.20570944017448</v>
       </c>
       <c r="AO12" t="n">
-        <v>2.25950232790062</v>
+        <v>1.13064796511604</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.648867834630464</v>
+        <v>69.5078139826724</v>
       </c>
       <c r="AQ12" t="n">
-        <v>148.487742800499</v>
+        <v>-0.0128544574122275</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.0149294790049</v>
+        <v>0.0344414747163138</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0.257622881469422</v>
+        <v>-0.25086384606443</v>
       </c>
       <c r="AT12" t="n">
-        <v>-1.89093861852215</v>
+        <v>0.0495522387392417</v>
       </c>
       <c r="AU12" t="n">
-        <v>-1.82212425048548</v>
+        <v>-0.0605144058354366</v>
       </c>
       <c r="AV12" t="n">
-        <v>-1.53857532118651</v>
+        <v>0.0302788951199366</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.62929712827602</v>
+        <v>0.0059130078110877</v>
       </c>
       <c r="AX12" t="n">
-        <v>-1.14753971794914</v>
+        <v>0.283442369376223</v>
       </c>
       <c r="AY12" t="n">
-        <v>-1.17514059004626</v>
+        <v>1.25678752951199</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-1.33286892706426</v>
+        <v>0.198449042386782</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.0696894773037612</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0.00942422520285237</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0.00110592499070373</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.0122694085372572</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.265324252837569</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0150512726830773</v>
+        <v>-0.0200155193338293</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.223234907343688</v>
+        <v>-0.330280240826589</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.236885852590978</v>
+        <v>-0.163792050368117</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.232157150714152</v>
+        <v>-0.167271902499466</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.104267758443802</v>
+        <v>-0.0851775313067445</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.150777291611823</v>
+        <v>-0.0508814655739771</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0493302139716222</v>
+        <v>-0.111206748686996</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.155277208507116</v>
+        <v>-0.133451925871853</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.218487319719277</v>
+        <v>-0.237554391414924</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.00303514115906172</v>
+        <v>-0.170995817172662</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.150768462335359</v>
+        <v>-0.162021848639044</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.104731402214584</v>
+        <v>-0.123243924866692</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.269681043265435</v>
+        <v>-0.186937087540904</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.162699525471072</v>
+        <v>-0.116101471196711</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.142777814264526</v>
+        <v>-0.146379752900888</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.0276081410003373</v>
+        <v>-0.0352814659320229</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.208597045327139</v>
+        <v>-0.172749983022184</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.14153724253889</v>
+        <v>-0.127267221710903</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.142593542356211</v>
+        <v>-0.150969210942737</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.208000306186802</v>
+        <v>-0.16932861076034</v>
       </c>
       <c r="V13" t="n">
-        <v>0.265103922560545</v>
+        <v>0.0259254616774935</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.000372952903307736</v>
+        <v>-0.0684190765815336</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0418095227298719</v>
+        <v>-0.0200155193338293</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.0356794218862955</v>
+        <v>-0.63488960520175</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.0096919104076664</v>
+        <v>-8.88016008611467</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.03548416424113</v>
+        <v>10.5718083691601</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.158826364408112</v>
+        <v>-10.3132268136898</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.453590897977316</v>
+        <v>0.235458545872261</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.111027664953521</v>
+        <v>1.06512778425032</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.0294895642637357</v>
+        <v>1.04478329645459</v>
       </c>
       <c r="AF13" t="n">
-        <v>-6.99189680619992</v>
+        <v>1.2436250193625</v>
       </c>
       <c r="AG13" t="n">
-        <v>10.1827511078116</v>
+        <v>-0.296919982786842</v>
       </c>
       <c r="AH13" t="n">
-        <v>-10.8241320982122</v>
+        <v>1.07400427593327</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.00622260224435605</v>
+        <v>0.837274531912688</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.000505477607933447</v>
+        <v>1.8697104870729</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.0027543121170055</v>
+        <v>-0.0200155193338293</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.0321178268841117</v>
+        <v>-3.68921628388639</v>
       </c>
       <c r="AM13" t="n">
-        <v>-3.08807048318361</v>
+        <v>2.44971914892797</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.31425553187271</v>
+        <v>-0.698329443036231</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.51726564692218</v>
+        <v>-0.587401204304756</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.238469797894641</v>
+        <v>-10.837588555778</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.3295750591238</v>
+        <v>-0.00604218862407214</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.0185730582856031</v>
+        <v>-0.0200155193338293</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.209236706958569</v>
+        <v>0.213124797157149</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.02590249074353</v>
+        <v>-0.0127727968714012</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.00655734332769</v>
+        <v>0.0412324619215205</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.19099029710674</v>
+        <v>-0.0332358585826731</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.307647700898158</v>
+        <v>-0.0110129494685375</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01588745033623</v>
+        <v>-0.148420789500691</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.787189130540361</v>
+        <v>-0.513037522362324</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.80222559297986</v>
+        <v>-0.11121142822194</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.0347804888684874</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.00934096752396569</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.00115267060212793</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-0.00141794201922911</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0.0459642948242026</v>
       </c>
     </row>
   </sheetData>

--- a/sum.var_AMR_ES_FQ_R.xlsx
+++ b/sum.var_AMR_ES_FQ_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">log_AMC_ville_tot_except_FQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prescri_1</t>
   </si>
   <si>
     <t xml:space="preserve">AMR_animaux_compagnie_C3G_R</t>
@@ -719,10 +722,13 @@
       <c r="BE1" t="s">
         <v>56</v>
       </c>
+      <c r="BF1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" t="n">
         <v>0.00732955410328057</v>
@@ -785,117 +791,120 @@
         <v>-0.114851315499916</v>
       </c>
       <c r="V2" t="n">
+        <v>0.0783652775785313</v>
+      </c>
+      <c r="W2" t="n">
         <v>-0.00704050577408892</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>-0.0332588684908322</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>0.00732955410328057</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>0.0582695830019245</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>-12.3303494649166</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>-4.38486917941033</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>-18.8678731402826</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>0.130610908822835</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>0.375555392934203</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>0.357498405731887</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>0.152621661124171</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>0.150973298446975</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>-0.346688833462624</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AJ2" t="n">
         <v>0.235349613528001</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>-0.209548982113039</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>0.00732955410328057</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>2.46131616730103</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AN2" t="n">
         <v>-2.19227167052624</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AO2" t="n">
         <v>-0.14689466098425</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>0.464358721866095</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
         <v>11.0218902694913</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>-0.0137138057235682</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>0.00732955410328057</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>-0.0976156339794002</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>0.0711842396775379</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AV2" t="n">
         <v>0.0133997267485429</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AW2" t="n">
         <v>-0.0134887005011725</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AX2" t="n">
         <v>-0.0116735390973381</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AY2" t="n">
         <v>-0.23814057256977</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="AZ2" t="n">
         <v>0.102157056829545</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BA2" t="n">
         <v>0.100964937158633</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BB2" t="n">
         <v>0.010521087269544</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BC2" t="n">
         <v>0.00535566593062078</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BD2" t="n">
         <v>0.00172099403356767</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BE2" t="n">
         <v>-0.00508228708977854</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BF2" t="n">
         <v>-0.073997723673461</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B3" t="n">
         <v>-0.0448804961991626</v>
@@ -958,117 +967,120 @@
         <v>0.0175382891813646</v>
       </c>
       <c r="V3" t="n">
+        <v>-0.0332510477570974</v>
+      </c>
+      <c r="W3" t="n">
         <v>-0.0217683700198446</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>0.0791304082566166</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>-0.0448804961991626</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>-0.770302815554919</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>3.17771325978908</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>9.45590659332335</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>15.5290344904718</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>0.0786333169234391</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>0.44603511539236</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>0.420761142313532</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
         <v>0.117825175411432</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>-0.191019448211413</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
         <v>-0.603686124644861</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ3" t="n">
         <v>0.323806812980551</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>-0.671327616035061</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>-0.0448804961991626</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
         <v>-1.78849019467855</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AN3" t="n">
         <v>0.594774917323201</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
         <v>-1.71738724827605</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AP3" t="n">
         <v>-0.472378788154204</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AQ3" t="n">
         <v>-5.42457052529447</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AR3" t="n">
         <v>-0.00784936955362009</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AS3" t="n">
         <v>-0.0448804961991626</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AT3" t="n">
         <v>-0.0689272219917101</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
         <v>-0.124494038406793</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
         <v>0.0396977072599543</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
         <v>-0.0114595398085665</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AX3" t="n">
         <v>-0.00299484608859408</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AY3" t="n">
         <v>-0.0900985847101783</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AZ3" t="n">
         <v>-0.430405702605618</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BA3" t="n">
         <v>-0.0400073610756617</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BB3" t="n">
         <v>-0.0209620918427937</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BC3" t="n">
         <v>-0.00686645883417283</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BD3" t="n">
         <v>-0.00212758389752027</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BE3" t="n">
         <v>0.00960011029148658</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BF3" t="n">
         <v>-0.733223676197547</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" t="n">
         <v>-0.0402427339189276</v>
@@ -1131,117 +1143,120 @@
         <v>-0.0732747438842462</v>
       </c>
       <c r="V4" t="n">
+        <v>0.114914367516149</v>
+      </c>
+      <c r="W4" t="n">
         <v>-0.00278835022062918</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>-0.0963687065038142</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>-0.0402427339189276</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>-0.0055179876751338</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>-3.63618198377684</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>3.19198075695889</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>12.7284237561243</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>0.282585669768487</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>1.08459192358979</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>1.08405563486571</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>1.69130769280195</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>-0.369642789809718</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>2.74556373901538</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
         <v>0.75630921144054</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>2.08339580005781</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>-0.0402427339189276</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>-4.31875399729239</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
         <v>3.56540005694909</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>-0.782589675263861</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>-1.41801144666476</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AQ4" t="n">
         <v>-42.063917768553</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
         <v>0.00319752936881097</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
         <v>-0.0402427339189276</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AT4" t="n">
         <v>0.391618492627779</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>-0.0654341902052057</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
         <v>0.0180099487089462</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AW4" t="n">
         <v>-0.0322092704598475</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AX4" t="n">
         <v>-0.017640294352863</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AY4" t="n">
         <v>0.271938752196663</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="AZ4" t="n">
         <v>0.0988875903309765</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BA4" t="n">
         <v>-0.110766501464643</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BB4" t="n">
         <v>-0.041946136308274</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BC4" t="n">
         <v>-0.00273756632938549</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BD4" t="n">
         <v>-0.00197807540185887</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BE4" t="n">
         <v>0.00639467520062348</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BF4" t="n">
         <v>-0.00507901594179504</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" t="n">
         <v>-0.00323860940402544</v>
@@ -1304,117 +1319,120 @@
         <v>-0.0662767394077226</v>
       </c>
       <c r="V5" t="n">
+        <v>0.0296737136920025</v>
+      </c>
+      <c r="W5" t="n">
         <v>-0.0175848898050814</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>-0.000922632744525248</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>-0.00323860940402544</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>-0.602380310114915</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>12.8592769993275</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>-0.192251643736603</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>26.77912495624</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>-0.197700988707845</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>-0.480525696225354</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>-0.491243416945087</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>-0.517661915067306</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>-0.284096832305203</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
         <v>-0.268031660005875</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
         <v>-0.416594915570839</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
         <v>-0.311494422645666</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AL5" t="n">
         <v>-0.00323860940402544</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AM5" t="n">
         <v>-3.27804295023073</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AN5" t="n">
         <v>0.103643179064499</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AO5" t="n">
         <v>-1.31587084830012</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AP5" t="n">
         <v>-0.38010878600959</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AQ5" t="n">
         <v>-6.61747476724499</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AR5" t="n">
         <v>0.0379833337977912</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AS5" t="n">
         <v>-0.00323860940402544</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AT5" t="n">
         <v>-0.0623337941018985</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
         <v>-0.0889789398903094</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
         <v>0.0267904630273537</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="n">
         <v>-0.011307532303508</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AX5" t="n">
         <v>0.000275088542728966</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
         <v>-0.498774154428945</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="AZ5" t="n">
         <v>-0.805735820374807</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BA5" t="n">
         <v>-0.120788240069277</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BB5" t="n">
         <v>-0.0302881325843596</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BC5" t="n">
         <v>0.0000407778520189205</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BD5" t="n">
         <v>-0.000485969982432017</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BE5" t="n">
         <v>0.00829966907346026</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BF5" t="n">
         <v>-0.622655757258443</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" t="n">
         <v>0.0196401513701033</v>
@@ -1477,117 +1495,120 @@
         <v>0.0248295369766438</v>
       </c>
       <c r="V6" t="n">
+        <v>-0.0694984089622275</v>
+      </c>
+      <c r="W6" t="n">
         <v>-0.0202219764604383</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>0.0597279019483435</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>0.0196401513701033</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>-0.423678741868557</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>-2.61132807038946</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>-6.89076795398724</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>-29.9470519040486</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>-0.0332608460612143</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>0.137839947010808</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
         <v>0.13637941094463</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AG6" t="n">
         <v>-0.122399969203203</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AH6" t="n">
         <v>-0.150794157450055</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AI6" t="n">
         <v>-0.388364951192247</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AJ6" t="n">
         <v>-0.0224633016088872</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AK6" t="n">
         <v>-0.595670602562299</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AL6" t="n">
         <v>0.0196401513701033</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AM6" t="n">
         <v>0.647163158559724</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AN6" t="n">
         <v>-3.1904011933925</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AO6" t="n">
         <v>-0.453595963951475</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AP6" t="n">
         <v>0.622946781722748</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AQ6" t="n">
         <v>-15.8994468340273</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AR6" t="n">
         <v>-0.00455811689816679</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AS6" t="n">
         <v>0.0196401513701033</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AT6" t="n">
         <v>-0.0650535239568293</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
         <v>-0.0879917342022967</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
         <v>0.0198687079575747</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AW6" t="n">
         <v>0.00373493005830028</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AX6" t="n">
         <v>0.00822729452788746</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AY6" t="n">
         <v>0.0877323322809686</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AZ6" t="n">
         <v>-0.190653634970529</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BA6" t="n">
         <v>0.0388954366948321</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BB6" t="n">
         <v>0.0118321019448495</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BC6" t="n">
         <v>-0.00503272571077103</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BD6" t="n">
         <v>-0.000799265942887367</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BE6" t="n">
         <v>-0.00593181281709199</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BF6" t="n">
         <v>-0.242091355144987</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B7" t="n">
         <v>0.0188915953450621</v>
@@ -1650,117 +1671,120 @@
         <v>0.111511245163811</v>
       </c>
       <c r="V7" t="n">
+        <v>0.0276913164771287</v>
+      </c>
+      <c r="W7" t="n">
         <v>-0.000156771078757567</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>0.117467098864332</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>0.0188915953450621</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>0.138826687668009</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>-4.93482380993126</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>-7.22063560926808</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>19.8455533951558</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>-0.0180925555466997</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>0.418246721515095</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
         <v>0.424361583032095</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
         <v>0.289059744010996</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AH7" t="n">
         <v>-0.271578415094269</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AI7" t="n">
         <v>0.308994584925497</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AJ7" t="n">
         <v>0.159101834134017</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AK7" t="n">
         <v>0.197995368697023</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AL7" t="n">
         <v>0.0188915953450621</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AM7" t="n">
         <v>1.12134033295021</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
         <v>-5.94298722785559</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AO7" t="n">
         <v>2.15545868450043</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AP7" t="n">
         <v>1.54602068082667</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AQ7" t="n">
         <v>-32.1995523411849</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AR7" t="n">
         <v>-0.0121944982685219</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AS7" t="n">
         <v>0.0188915953450621</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AT7" t="n">
         <v>-0.170172304400208</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>-0.130900303696153</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
         <v>-0.0097474141827183</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AW7" t="n">
         <v>0.0367801772712077</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AX7" t="n">
         <v>0.0262124964709996</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AY7" t="n">
         <v>0.357638558366775</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="AZ7" t="n">
         <v>-0.563513299647262</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BA7" t="n">
         <v>-0.106189643756344</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BB7" t="n">
         <v>-0.0501937303954304</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BC7" t="n">
         <v>0.0165749855340629</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BD7" t="n">
         <v>0.00341200918641746</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BE7" t="n">
         <v>-0.0185588523633794</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BF7" t="n">
         <v>0.420820327277151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" t="n">
         <v>0.0533533633004615</v>
@@ -1823,117 +1847,120 @@
         <v>0.0918117366690664</v>
       </c>
       <c r="V8" t="n">
+        <v>0.00189803511554691</v>
+      </c>
+      <c r="W8" t="n">
         <v>0.0317868662453055</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>-0.0612103131719041</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>0.0533533633004615</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>1.71905337412741</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>-9.01272307721351</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>-16.3377612856515</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>-92.0387708878531</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>-0.324050522133134</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>-1.96214937859133</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
         <v>-1.89546618886632</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
         <v>-1.89651190208578</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AH8" t="n">
         <v>-0.537245017539383</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
         <v>-1.22021097105653</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AJ8" t="n">
         <v>-1.22631695627796</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AK8" t="n">
         <v>-0.810419476847576</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AL8" t="n">
         <v>0.0533533633004615</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AM8" t="n">
         <v>11.0611048510848</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AN8" t="n">
         <v>-8.13657157043532</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AO8" t="n">
         <v>1.89965622981696</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AP8" t="n">
         <v>1.2231669853248</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AQ8" t="n">
         <v>-14.3772288344109</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
         <v>0.0167786207189275</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AS8" t="n">
         <v>0.0533533633004615</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AT8" t="n">
         <v>-0.160721921099835</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>0.623368914024887</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
         <v>-0.104572526869896</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AW8" t="n">
         <v>0.0145650987656854</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AX8" t="n">
         <v>-0.00235061950876203</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AY8" t="n">
         <v>-0.364227869492569</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="AZ8" t="n">
         <v>0.868083983240932</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BA8" t="n">
         <v>0.332517882452744</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BB8" t="n">
         <v>0.103648576807794</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BC8" t="n">
         <v>0.0175497742443751</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BD8" t="n">
         <v>0.00697314120095147</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BE8" t="n">
         <v>-0.0301335771134524</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BF8" t="n">
         <v>2.10000862327134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" t="n">
         <v>-0.0383343059783089</v>
@@ -1996,117 +2023,120 @@
         <v>0.0416848994848347</v>
       </c>
       <c r="V9" t="n">
+        <v>0.0247461477456109</v>
+      </c>
+      <c r="W9" t="n">
         <v>-0.00113998729489261</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>-0.0674828256708319</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>-0.0383343059783089</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>-0.314908419026853</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>-0.624784079803963</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>24.7971160064304</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>21.1224527119021</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>0.229753807778225</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>1.05828541957378</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
         <v>1.06438261422827</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
         <v>0.785942009562261</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AH9" t="n">
         <v>-0.239068858776235</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
         <v>0.487882730365099</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AJ9" t="n">
         <v>0.697195612240213</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AK9" t="n">
         <v>-0.0374455911788562</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AL9" t="n">
         <v>-0.0383343059783089</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AM9" t="n">
         <v>-1.67028852900829</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AN9" t="n">
         <v>-0.0109312412913779</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AO9" t="n">
         <v>-0.191921675231057</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AP9" t="n">
         <v>-0.336248048840461</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AQ9" t="n">
         <v>-38.3424138223202</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AR9" t="n">
         <v>-0.00107446016607559</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AS9" t="n">
         <v>-0.0383343059783089</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
         <v>0.074872943332801</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>-0.085804112752481</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
         <v>0.0321586612015137</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AW9" t="n">
         <v>-0.00673117719952007</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AX9" t="n">
         <v>0.00173258813346108</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AY9" t="n">
         <v>-0.0206447053958451</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="AZ9" t="n">
         <v>-0.56047013214129</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BA9" t="n">
         <v>-0.0657887445398481</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BB9" t="n">
         <v>-0.0496410442958685</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BC9" t="n">
         <v>0.00197200880993254</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BD9" t="n">
         <v>-0.000229650166180577</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BE9" t="n">
         <v>0.000208184884516435</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BF9" t="n">
         <v>-0.10211662579286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" t="n">
         <v>-0.00601199919180279</v>
@@ -2169,117 +2199,120 @@
         <v>0.0274333514639498</v>
       </c>
       <c r="V10" t="n">
+        <v>-0.0338589119520969</v>
+      </c>
+      <c r="W10" t="n">
         <v>-0.00351881208243151</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>0.000139235351569367</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>-0.00601199919180279</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>-0.317730159419209</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>9.18564175834393</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>2.60351806295416</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>38.9228280039465</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>-0.0079908077062404</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>0.0993371854900619</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
         <v>0.0648298521035288</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
         <v>0.120572232824682</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
         <v>0.598748291963005</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>-0.117960350491315</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AJ10" t="n">
         <v>0.0824821535077846</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AK10" t="n">
         <v>0.322043412432475</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AL10" t="n">
         <v>-0.00601199919180279</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AM10" t="n">
         <v>-3.36054905774655</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AN10" t="n">
         <v>0.125640023711585</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AO10" t="n">
         <v>-1.05862112080309</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AP10" t="n">
         <v>-0.969569942067806</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AQ10" t="n">
         <v>20.4716391934634</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AR10" t="n">
         <v>0.00616639835771458</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AS10" t="n">
         <v>-0.00601199919180279</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AT10" t="n">
         <v>0.123513363905274</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>-0.0682606175468987</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
         <v>0.00640762906621618</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
         <v>-0.00569589876732141</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AX10" t="n">
         <v>-0.00231622520835979</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AY10" t="n">
         <v>0.226721715917034</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="AZ10" t="n">
         <v>0.255688366175892</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BA10" t="n">
         <v>-0.106329782035779</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BB10" t="n">
         <v>0.000487602492993006</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BC10" t="n">
         <v>-0.01638452748375</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BD10" t="n">
         <v>-0.00423125097371813</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BE10" t="n">
         <v>0.0154679259900934</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BF10" t="n">
         <v>-0.544121789461287</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B11" t="n">
         <v>0.0190675251908354</v>
@@ -2342,117 +2375,120 @@
         <v>0.0233233898465209</v>
       </c>
       <c r="V11" t="n">
+        <v>-0.134269002145114</v>
+      </c>
+      <c r="W11" t="n">
         <v>-0.0160402896903781</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>0.1346138312419</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>0.0190675251908354</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>0.128949509529747</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>6.42513956495643</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>-3.78655200623572</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>28.9449742236903</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>-0.0951203534760066</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>-0.280465339930393</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>-0.315517269456471</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
         <v>-0.268724626977033</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>0.975430705687471</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>-0.489446482450284</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AJ11" t="n">
         <v>-0.198475120765655</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AK11" t="n">
         <v>-0.48313178901756</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AL11" t="n">
         <v>0.0190675251908354</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AM11" t="n">
         <v>-1.42640909208072</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AN11" t="n">
         <v>5.91211095973774</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AO11" t="n">
         <v>-0.895613718645758</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AP11" t="n">
         <v>-0.823422918814776</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AQ11" t="n">
         <v>64.7608500031866</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AR11" t="n">
         <v>-0.00583898559699208</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AS11" t="n">
         <v>0.0190675251908354</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AT11" t="n">
         <v>0.0725586485713087</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>-0.0794686588701281</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>-0.022730959003571</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>0.028768876407479</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AX11" t="n">
         <v>0.00562799823828984</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AY11" t="n">
         <v>0.132832947960337</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="AZ11" t="n">
         <v>0.482211586012499</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BA11" t="n">
         <v>-0.00974559752949912</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BB11" t="n">
         <v>0.0316327784762719</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BC11" t="n">
         <v>-0.0103886763340441</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BD11" t="n">
         <v>-0.00230109366776357</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BE11" t="n">
         <v>0.00888449742549417</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BF11" t="n">
         <v>-0.416902965091475</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" t="n">
         <v>0.0344414747163138</v>
@@ -2515,117 +2551,120 @@
         <v>0.0855989607660336</v>
       </c>
       <c r="V12" t="n">
+        <v>-0.193983119750397</v>
+      </c>
+      <c r="W12" t="n">
         <v>0.0325476245037432</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>-0.0634160524993205</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>0.0344414747163138</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>1.02430888453424</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>10.3825789897294</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>-11.8074921105374</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>-12.7054687916566</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>-0.280826175534107</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>-1.96187907500934</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AF12" t="n">
         <v>-1.89482506440636</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AG12" t="n">
         <v>-1.59565512176468</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
         <v>0.615213205875665</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
         <v>-1.18205595693551</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AJ12" t="n">
         <v>-1.22766947552045</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AK12" t="n">
         <v>-1.35410658786014</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AL12" t="n">
         <v>0.0344414747163138</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AM12" t="n">
         <v>4.24082559502784</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AN12" t="n">
         <v>6.72187461778694</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AO12" t="n">
         <v>3.20570944017448</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AP12" t="n">
         <v>1.13064796511604</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AQ12" t="n">
         <v>69.5078139826724</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AR12" t="n">
         <v>-0.0128544574122275</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AS12" t="n">
         <v>0.0344414747163138</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AT12" t="n">
         <v>-0.25086384606443</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>0.0495522387392417</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>-0.0605144058354366</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AW12" t="n">
         <v>0.0302788951199366</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AX12" t="n">
         <v>0.0059130078110877</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AY12" t="n">
         <v>0.283442369376223</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="AZ12" t="n">
         <v>1.25678752951199</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BA12" t="n">
         <v>0.198449042386782</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BB12" t="n">
         <v>0.0696894773037612</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BC12" t="n">
         <v>-0.00942422520285237</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BD12" t="n">
         <v>-0.00110592499070373</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BE12" t="n">
         <v>0.0122694085372572</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BF12" t="n">
         <v>0.265324252837569</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" t="n">
         <v>-0.0200155193338293</v>
@@ -2688,111 +2727,114 @@
         <v>-0.16932861076034</v>
       </c>
       <c r="V13" t="n">
+        <v>0.187571632441963</v>
+      </c>
+      <c r="W13" t="n">
         <v>0.0259254616774935</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>-0.0684190765815336</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>-0.0200155193338293</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>-0.63488960520175</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>-8.88016008611467</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>10.5718083691601</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>-10.3132268136898</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>0.235458545872261</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>1.06512778425032</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AF13" t="n">
         <v>1.04478329645459</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AG13" t="n">
         <v>1.2436250193625</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
         <v>-0.296919982786842</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AI13" t="n">
         <v>1.07400427593327</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AJ13" t="n">
         <v>0.837274531912688</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AK13" t="n">
         <v>1.8697104870729</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AL13" t="n">
         <v>-0.0200155193338293</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AM13" t="n">
         <v>-3.68921628388639</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AN13" t="n">
         <v>2.44971914892797</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AO13" t="n">
         <v>-0.698329443036231</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AP13" t="n">
         <v>-0.587401204304756</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AQ13" t="n">
         <v>-10.837588555778</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AR13" t="n">
         <v>-0.00604218862407214</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AS13" t="n">
         <v>-0.0200155193338293</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AT13" t="n">
         <v>0.213124797157149</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>-0.0127727968714012</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
         <v>0.0412324619215205</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AW13" t="n">
         <v>-0.0332358585826731</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
         <v>-0.0110129494685375</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AY13" t="n">
         <v>-0.148420789500691</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="AZ13" t="n">
         <v>-0.513037522362324</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BA13" t="n">
         <v>-0.11121142822194</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BB13" t="n">
         <v>-0.0347804888684874</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BC13" t="n">
         <v>0.00934096752396569</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BD13" t="n">
         <v>0.00115267060212793</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BE13" t="n">
         <v>-0.00141794201922911</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BF13" t="n">
         <v>-0.0459642948242026</v>
       </c>
     </row>
